--- a/www/download/COUNTRY.DNK.WIOD13.xlsx
+++ b/www/download/COUNTRY.DNK.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Dinamarca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.59534474692871</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5.79710144928534</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>6.59587093480106</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>6.69075326805805</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>6.96718477441534</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>8.05866701654832</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>8.31600818352559</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>7.8696784336552</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>6.5754865977623</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.98515681095156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5.98658985658789</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>5.94106463603802</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>5.4359641756125</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.07318051311202</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.34659312671883</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.553</t>
+          <t>-0.291944678346969</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.584</t>
+          <t>-0.270214479052244</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>-0.0295553343253024</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.668</t>
+          <t>-0.120013484602415</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>-0.14137149004825</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>-0.0934120695494324</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.742</t>
+          <t>-0.130124251652871</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.746</t>
+          <t>-0.155851583139991</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.714</t>
+          <t>-0.26497532368705</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>-0.270076391351688</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.727</t>
+          <t>-0.255224335452692</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>-0.256053851837141</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.861</t>
+          <t>-0.257934324794992</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.907</t>
+          <t>-0.197304356669184</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t>-0.115259999604788</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.352</t>
+          <t>-0.13922791975748</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.386</t>
+          <t>-0.11645008539367</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.434</t>
+          <t>0.159735979917159</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>0.0695605924218721</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>0.0499509027950769</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.527</t>
+          <t>0.126287350700115</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.561</t>
+          <t>0.0866166654090192</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0486316408103813</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>-0.0970488870586572</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>-0.100283664151297</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.554</t>
+          <t>-0.101364093238597</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-0.109350756388247</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>-0.102924372656117</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>-0.0326247815496727</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.651</t>
+          <t>0.0804138355871742</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3946.525</t>
+          <t>0.0959098423997979</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3968.857</t>
+          <t>0.12359997426695</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4069.596</t>
+          <t>0.459260011548952</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4172.171</t>
+          <t>0.356096409415584</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4237.91</t>
+          <t>0.339199815418419</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4300.641</t>
+          <t>0.448840706200548</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4354.175</t>
+          <t>0.4042664768995</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4335.214</t>
+          <t>0.349027647716327</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4278.018</t>
+          <t>0.216398099910719</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4260.686</t>
+          <t>0.227755302417369</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4305.218</t>
+          <t>0.205210305767318</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4413.431</t>
+          <t>0.239821792156942</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>4490.221</t>
+          <t>0.150455566833504</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4563.611</t>
+          <t>0.238856508693118</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4426.213</t>
+          <t>0.375310996936803</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3561.707</t>
+          <t>7176372993.99584</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3580.474</t>
+          <t>7110274800.72969</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3694.916</t>
+          <t>7476410589.85481</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3793.961</t>
+          <t>6865820906.90928</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3866.816</t>
+          <t>6513929634.64433</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3914.097</t>
+          <t>6513008475.51102</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3978.711</t>
+          <t>6669328288.34484</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3945.645</t>
+          <t>6528826981.60018</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3897.167</t>
+          <t>6927218659.637</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3895.572</t>
+          <t>7085008646.72914</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3953.214</t>
+          <t>6922369259.08324</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4060.536</t>
+          <t>7066280058.36237</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4152.28</t>
+          <t>7217451400.25665</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4239.784</t>
+          <t>6674827469.35336</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4075.162</t>
+          <t>5664522040.84815</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>4160073931.75761</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>4081528739.86127</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>3213291967.70831</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>3599752033.3781</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>3750617029.96831</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>3559304165.71013</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>3764316466.72799</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>3878518119.12255</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>4406906402.79272</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>4426142633.02633</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>4475971389.54086</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>4608643621.25642</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>4669699708.97944</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>4450391826.49546</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>3841262157.65359</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55.06</t>
+          <t>935994.677743533</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>917055.131404494</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>1056197.59564336</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>969507.97096288</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>935742.07423448</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>55.47</t>
+          <t>970879.504975657</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>55.35</t>
+          <t>1008600.20808726</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>916666.173190581</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>814971.708002424</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>51.69</t>
+          <t>747763.624019737</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>698075.357312235</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>639881.197547818</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>563977.35609492</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>476674.788117912</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>45.08</t>
+          <t>481040.474101487</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>17377.3600788698</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>17366.4938579878</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17571.9142307693</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>17856.4989317854</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>18357.891325303</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>19280.5221830309</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>18828.0716859829</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>19092.4072637979</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>20155.4652736724</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>21892.9734285964</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>23523.9667635648</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>25145.9289697243</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>28616.9911635062</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>31838.5225907495</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>29226.0796986834</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>55870.0233445572</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>55766.9862771174</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>58262.0679184369</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>53210.37480043</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>51579.4094448821</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>53659.1679626388</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>53507.2232963952</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>53548.6245387652</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>61199.8668963427</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>68981.7001479665</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>72183.2171556246</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>77225.2081363318</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>89233.851264998</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>91364.5043217491</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>72324.0497200934</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>-0.143835648494065</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>-0.122761536619317</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>54.96</t>
+          <t>0.149884927087773</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>0.0539506512729584</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55.53</t>
+          <t>0.0309812943052392</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.0996803919451164</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>0.0569544391835801</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>0.017307352657834</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>-0.115668307016842</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>51.81</t>
+          <t>-0.119872014305954</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>-0.116791941691676</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>-0.118930354850695</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>-0.110803636470346</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>-0.0473235291871613</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>0.060891348553175</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>43726.5058234011</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>42500.2270272354</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>37455.5968091088</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>37193.7255074607</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>33968.7520381638</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>32043.5127684453</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>31044.5094679887</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>32753.127764187</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>38654.3286683495</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>43786.9047660551</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>43252.9336182844</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>44137.7391093515</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>49827.6946427098</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.59534474692871</t>
+          <t>1768.5952933914</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.79710144928534</t>
+          <t>1710.81704922553</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.59587093480106</t>
+          <t>1320.20125701827</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6.69075326805805</t>
+          <t>1452.89316519165</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.96718477441534</t>
+          <t>1497.89152734972</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.05866701654832</t>
+          <t>1408.39773556204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.31600818352559</t>
+          <t>1470.07491781433</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.8696784336552</t>
+          <t>1515.2722473129</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6.5754865977623</t>
+          <t>1741.78519691947</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.98515681095156</t>
+          <t>1753.95792183145</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5.98658985658789</t>
+          <t>1752.66009357795</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.94106463603802</t>
+          <t>1765.45539218298</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.4359641756125</t>
+          <t>1737.3577550032</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.07318051311202</t>
+          <t>1628.53146460259</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5.34659312671883</t>
+          <t>1449.21695681983</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>4948240338.18638</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>4972917897.64972</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>3934384474.94095</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>3874565050.98072</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>4611221383.91339</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>4567802388.70529</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>4884790218.161</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>4946122231.30384</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>5920326941.60605</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>5909098956.18863</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>6007149516.29585</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>5780381297.36041</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>5625582065.51891</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>5856718542.08864</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>4967780806.68811</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>5698146940.18008</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>5690070765.76128</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>4587017939.89511</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>4558840140.12909</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>5375998636.85305</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>5692975538.08407</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>6126502393.52997</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>6249009915.2529</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>7286691445.28855</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>7494099830.07963</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>7649437129.00699</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>7491449209.27432</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>7577445504.95362</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>7865788853.83966</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>6918083759.18893</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>-749906601.993692</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-717152868.111564</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>-652633464.954154</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>-684275089.148371</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>-764777252.939666</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-1125173149.37878</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-1241712175.36897</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-1302887683.94906</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>-1366364503.6825</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-1585000873.89099</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>-1642287612.71114</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>-1711067911.9139</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>-1951863439.43471</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2009070311.75101</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1950302952.50082</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>1514.2082424429</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>1500.79451938808</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>1518.07952616764</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>1531.27769768377</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1544.29814559586</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>1548.78737385748</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1553.80221031629</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>1541.49759846977</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>1540.3158520048</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1543.70745273363</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>1547.96351812347</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>1555.48915591759</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>1544.85219789889</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1551.46360830526</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>1537.46173166672</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>1546.00536524904</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>1535.8664239531</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>1548.68038951466</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>1563.72010707221</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>1573.25732435887</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>1585.49210763813</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>1587.68083574144</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1578.76079768096</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>1576.54561073196</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>1579.41120430361</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>1578.78875445926</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>1585.59509156609</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>1569.56885121954</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>1569.61069362401</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>1549.55473298394</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-29.2</t>
+          <t>63435.7198688412</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-27.03</t>
+          <t>64834.8321353354</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>59901.0402145433</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>59002.918688465</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>63789.1418136659</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>68026.8757360042</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>68753.7176463007</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>72415.7853827395</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-26.5</t>
+          <t>85723.8896220672</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>98085.0182609527</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>112538.837149356</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-25.61</t>
+          <t>128101.820149994</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-25.8</t>
+          <t>147311.572262702</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-19.73</t>
+          <t>172483.935431814</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>133160.800462652</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>2805259844.35044</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>2826489705.48765</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>2939656659.97028</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>2610248847.59146</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>2606140072.52167</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>2589753306.83498</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2701184194.98476</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>2594835954.45785</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>2740471662.93514</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>2790173626.73335</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>2710701124.03592</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>2887923337.68999</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>2885881503.8559</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>2789378344.79613</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>2252140144.88736</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>53811.4976921497</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>53513.5597832022</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>50842.6571843734</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>52477.1155841272</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>52539.4291892659</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>56304.4997621318</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>56392.820255366</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>60285.701819875</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>69948.6046646054</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>83296.9080151088</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>96932.128610976</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>115795.462744549</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>135452.41609655</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>156527.12150155</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>117439.956803008</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3946.525</t>
+          <t>6267536683.03956</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3968.857</t>
+          <t>6121419365.92408</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4069.596</t>
+          <t>5634476169.23557</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4172.171</t>
+          <t>5544723230.98732</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4237.91</t>
+          <t>5525510171.69693</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4300.641</t>
+          <t>5417392118.9191</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4354.175</t>
+          <t>5656714386.01956</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4335.214</t>
+          <t>5668971260.26299</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4278.018</t>
+          <t>6363654971.65246</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4260.686</t>
+          <t>6724462900.6951</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4305.218</t>
+          <t>6786106396.67036</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4413.431</t>
+          <t>7278859105.77014</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4490.221</t>
+          <t>7331077445.18351</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4563.611</t>
+          <t>7240259152.28615</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4426.213</t>
+          <t>5696880571.54657</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3561.707</t>
+          <t>9624.22217669158</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3580.474</t>
+          <t>11321.2723521332</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3694.916</t>
+          <t>9058.38303016988</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3793.961</t>
+          <t>6525.8031043378</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3866.816</t>
+          <t>11249.7126244</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3914.097</t>
+          <t>11722.3759738724</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3978.711</t>
+          <t>12360.8973909347</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3945.645</t>
+          <t>12130.0835628645</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3897.167</t>
+          <t>15775.2849574618</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3895.572</t>
+          <t>14788.1102458439</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3953.214</t>
+          <t>15606.7085383796</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4060.536</t>
+          <t>12306.3574054449</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4152.28</t>
+          <t>11859.1561661517</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4239.784</t>
+          <t>15956.8139302642</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4075.162</t>
+          <t>15720.8436596438</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7177.503</t>
+          <t>-3462276838.68912</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7111.921</t>
+          <t>-3294929660.43644</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7479.513</t>
+          <t>-2694819509.26529</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6864.353</t>
+          <t>-2934474383.39586</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6434.922</t>
+          <t>-2919370099.17526</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6513.323</t>
+          <t>-2827638812.08412</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6669.451</t>
+          <t>-2955530191.03479</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6529.867</t>
+          <t>-3074135305.80514</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6928.405</t>
+          <t>-3623183308.71731</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7086.07</t>
+          <t>-3934289273.96175</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6921.36</t>
+          <t>-4075405272.63444</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7066.632</t>
+          <t>-4390935768.08014</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7219.343</t>
+          <t>-4445195941.32761</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>6675.1</t>
+          <t>-4450880807.49002</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5664.677</t>
+          <t>-3444740426.6592</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>76158.1308</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>77336.40736</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>71561.74027</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>71798.34376</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>72001.2481</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>68338.96983</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>67699.42724</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>72464.58774</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>87710.6187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>100475.73005</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>105203.46576</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>110691.77672</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>123787.42364</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>137405.3237</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>120509.42214</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2232.081</t>
+          <t>0.0141694148850497</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2214.223</t>
+          <t>0.0147411243579649</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2254.895</t>
+          <t>0.0188631031081301</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2304.053</t>
+          <t>0.0154569288444567</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2318.406</t>
+          <t>0.0210402400690933</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2340.219</t>
+          <t>0.0261025435430806</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2346.797</t>
+          <t>0.0252736069230795</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2327.81</t>
+          <t>0.0248086660555354</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2281.399</t>
+          <t>0.0264475921514043</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2248.595</t>
+          <t>0.0307038500778597</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2255.948</t>
+          <t>0.0338512671946493</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2300.909</t>
+          <t>0.0367598494220366</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2314.612</t>
+          <t>0.0334751332164377</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2326.031</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2289.028</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>94971.4486076223</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>96628.980039683</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>89063.7497972945</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>92950.5213038583</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>93612.2728596442</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>84412.844093664</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>86209.8718097497</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>94381.1111311811</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>115950.35382168</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>131238.165489814</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>137583.502637156</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>146652.503161933</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>170947.778596475</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>192843.389463581</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>184367.104605978</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4160.407</t>
+          <t>103620.007425453</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4081.915</t>
+          <t>105475.073243332</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3213.837</t>
+          <t>96758.6284176353</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3599.513</t>
+          <t>100831.035595434</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3695.606</t>
+          <t>101218.949515811</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3559.517</t>
+          <t>91433.6251083937</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3764.406</t>
+          <t>93025.9601306236</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3878.948</t>
+          <t>102246.71517741</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4407.181</t>
+          <t>125590.118048088</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4426.1</t>
+          <t>141688.54413748</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4475.854</t>
+          <t>148070.084821056</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4608.817</t>
+          <t>157652.834543269</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4670.344</t>
+          <t>182898.0467475</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4450.549</t>
+          <t>206255.911435343</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3841.368</t>
+          <t>196642.801807363</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>715381.910500846</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-12.28</t>
+          <t>709772.477686175</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>632367.628214615</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>631824.896483757</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>617201.332464887</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>550681.842535283</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>545429.626777945</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>579962.246506701</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>696232.369591542</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>776989.753922345</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>806714.107145036</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>826951.669697429</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>937322.41144249</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>103620.007425453</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>107478.314061647</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>110091.980918479</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>115257.242471884</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>118907.260944611</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>122273.834383458</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>124968.864195211</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>127043.999053328</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>128545.372161906</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.748</t>
+          <t>129168.433981206</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>134200.158010163</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>139609.194989764</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>146197.708638013</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>148501.834772705</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>146718.272109112</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>94971.4486076223</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>98437.1041364147</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>101225.25690119</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>105795.945888027</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>109542.071798057</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>112637.152021985</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>115656.904164777</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>116820.83945849</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>118078.377225152</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>119057.522886082</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>123814.229867481</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>129272.648164632</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>136062.616394368</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>137805.029282041</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>135438.121692759</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>53863.0489145471</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>52963.0713866682</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>49384.0125823647</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>46959.7979745664</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>46954.8162441893</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>46417.7095416063</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>44829.4834593764</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>47141.2174625898</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>57067.9984219124</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>67643.4816825199</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>70561.2284089439</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>74536.3579667307</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>81204.6872324998</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>88539.9696946574</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>71286.3013226369</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3561707000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3580474000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3694916000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3793961000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3866816000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3914097000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3978711000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3945645000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3897167000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3895572000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3953214000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4060536000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4152280000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4239783579</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4075161790.5794</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3946525000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3968857000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4069596000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4172171000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4237910000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4300641000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4354175000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4335214000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4278018000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4260686000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4305218000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4413431000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4490221000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4563611344.86316</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4426213429.23584</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2232081000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2214223000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2254895000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2304053000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2318406000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2340219000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2346797000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2327810000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2281399000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2248595000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2255948000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2300909000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2314612000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2326030735.34952</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2289027968.72536</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2552724</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2584116</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2627783</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2668106</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2693717</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2712496</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2742475</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2745960</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2713539</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2697642</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2726912</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2783454</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2860799</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2907479.77406196</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2856442.13464624</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2352191</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2385719</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2433941</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2477644</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2503931</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2527201</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2560629</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2559618</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2530109</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2523517</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2553816</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2610456</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2687817</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2732763.79562092</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2650577.70651737</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3946525000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3968857000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4069596000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4172171000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4237910000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4300641000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4354175000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4335214000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4278018000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4260686000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4305218000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4413431000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4490221000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4563611344.86316</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4426213429.23584</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3561707000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3580474000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3694916000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3793961000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3866816000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3914097000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3978711000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3945645000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3897167000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3895572000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3953214000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4060536000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4152280000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4239783579</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4075161790.5794</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.223883473903054</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.23009214177032</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.236057132689494</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.245884667325644</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.250745961750358</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.255718720169047</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.263689990284609</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.268654797798724</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.299574972719611</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.302815111287093</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.313331495645102</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.318690099132054</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289584372171691</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.310858210514823</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.312893410037268</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.550590716553441</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.553503630601798</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.553976662936635</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.553250491018004</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.554990553961462</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.554732294142613</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.553521750790115</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.552981915247363</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.521002579797404</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.516869446873403</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.497784424326814</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.501836405989754</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466878590140647</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.466304492760894</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.450798377646792</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.225525809543505</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.216404227627882</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.209966204373871</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.200864841656351</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.19426348428818</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.18954898568834</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.182788258925276</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.178363286953914</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.179422447482985</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.180315441839504</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.188884080028084</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.179473494878193</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.243537037687662</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.222837296724283</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.236308212315941</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.184484225292462</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.191150044073375</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.197675761217595</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.204353656310667</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.208209712703704</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.209484889795474</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.216057403459574</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.223162201987542</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.249969179148038</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.252773922421227</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.265380467619703</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.268520250599075</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.240725825229757</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.264590109238242</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.266483772258316</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.543535941765506</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.547630426112232</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.549623609947919</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.551822541642323</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.555259003591729</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.557495429296252</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.557887924476222</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.55862712331648</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.523188138152505</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.518107901006387</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.500531128762789</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.498972650293365</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.463064097279716</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.462801473471055</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.446502858598185</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.271979832942032</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.261219529814393</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.252700628834487</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.24382380204701</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.236531283704567</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.233019680908274</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.226054672064205</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.218210674695979</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.226842682699457</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.229118176572386</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.234088403617508</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.23250709910756</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.296210077490528</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.272608417290703</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.287013369143499</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>298365.88747</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>300756.85585</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>278356.72166</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>283172.60081</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>285252.09168</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>269250.11318</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>273930.34712</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>295493.52028</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>357987.64963</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>410428.67847</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>444056.31049</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>484097.74638</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>561740.27321</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>630254.4631</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549075.19184</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>157483.05634</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>158438.14463</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>146142.641</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>147790.83357</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>148173.76576</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>137851.33465</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>137855.44359</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>149387.93264</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>182658.11647</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>209332.02582</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>218631.31323</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>232189.19251</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>264102.73398</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>294795.88113</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>267929.10313</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4002808.50525748</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4051529.22530515</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4122038.58445243</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4209363.92366684</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4297531.14459968</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4392592.39584807</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4488085.90693917</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4589482.40146926</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4676428.29878684</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4777350.63208677</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4898627.25363918</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5080876.73712512</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5275543.10240717</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
